--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A5030429-B196-493A-B9F0-4FC54CAE127E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D760AFCD-7F2E-4F1B-BB58-4EC8645ADD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S04aH03,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S05aH07,S01aH03,S05aH02,S05aH03,S05aH06,S05aH08,S01aH02,S04aH04,S03aH03,S03aH02,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH04,S02aH04,S02aH05,S06aH07,S04aH05,S04aH08</t>
+    <t>S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S05aH08,S03aH04,S04aH03,S04aH05,S04aH08,S03aH02,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S04aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH09,S05aH09,S06aH09,S03aH01,S02aH01,S02aH10,S05aH02,S01aH09,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH08,S02aH08,S02aH02,S04aH10,S06aH10,S04aH02,S01aH10,S03aH02,S01aH02,S05aH10,S02aH09,S04aH09,S05aH01,S03aH08,S03aH10,S06aH08,S05aH08</t>
+    <t>S03aH01,S06aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S05aH08,S04aH02,S01aH08,S02aH08,S01aH02,S05aH10,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH09,S05aH09,S06aH09,S03aH01,S02aH01,S02aH10,S05aH02,S01aH09,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01,S01aH08,S02aH08,S02aH02,S04aH10,S06aH10,S04aH02,S01aH10,S03aH02,S01aH02,S05aH10,S02aH09,S04aH09,S05aH01,S03aH08,S03aH10,S06aH08,S05aH08</v>
+        <v>S03aH01,S06aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S05aH08,S04aH02,S01aH08,S02aH08,S01aH02,S05aH10,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S04aH03,S01aH04,S01aH07,S02aH07,S01aH06,S02aH03,S05aH07,S01aH03,S05aH02,S05aH03,S05aH06,S05aH08,S01aH02,S04aH04,S03aH03,S03aH02,S04aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S03aH04,S02aH04,S02aH05,S06aH07,S04aH05,S04aH08</v>
+        <v>S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S05aH08,S03aH04,S04aH03,S04aH05,S04aH08,S03aH02,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CBDA78A2-FFB4-4B33-82AD-7CF6CD902EE4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3CF806-E6CD-435E-AAF9-1921C30FA6E2}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{27967B83-E866-4875-B5FC-87224AE1A629}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605BC8C7-63F4-48BA-99A1-0E36A0F248CD}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D716EEFD-D3F0-4F95-BE66-9408D35136E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59A4A8F-05CD-4CBC-9DAC-75EC43F0C477}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{064ABF91-8060-4786-975E-927DAB15FEB9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD68C9A-90A2-4402-97B0-4E8EEAAF3197}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EDB70C9-B0F4-430C-A239-75062F7057E7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CBFBE4-7347-4ADE-B758-844C58AA50B8}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32F0D1B4-456B-4E27-B192-B8AD9EC93ADA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0883D4F-7A33-495A-9007-9FD65445EB5F}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1770793-81FC-4307-88EB-A3A70078A096}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B846CDF-AE7D-49D8-AA17-24ECE0BBA512}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D760AFCD-7F2E-4F1B-BB58-4EC8645ADD6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{79556728-4942-44B1-AC07-F9BED8B351B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S05aH08,S03aH04,S04aH03,S04aH05,S04aH08,S03aH02,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S04aH02</t>
+    <t>S04aH02,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S03aH04,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S04aH06,S05aH04,S06aH02,S06aH03</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH01,S06aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S05aH08,S04aH02,S01aH08,S02aH08,S01aH02,S05aH10,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02</t>
+    <t>S01aH10,S03aH02,S04aH02,S05aH08,S03aH09,S05aH09,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH09,S06aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH01,S06aH09,S04aH08,S06aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S05aH08,S04aH02,S01aH08,S02aH08,S01aH02,S05aH10,S03aH09,S05aH09,S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02</v>
+        <v>S01aH10,S03aH02,S04aH02,S05aH08,S03aH09,S05aH09,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH09,S06aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH02,S06aH06,S04aH06,S05aH04,S06aH02,S06aH03,S05aH08,S03aH04,S04aH03,S04aH05,S04aH08,S03aH02,S01aH02,S04aH04,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH03,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S02aH04,S02aH05,S06aH07,S01aH06,S02aH03,S05aH07,S04aH02</v>
+        <v>S04aH02,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S03aH04,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S04aH06,S05aH04,S06aH02,S06aH03</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1A3CF806-E6CD-435E-AAF9-1921C30FA6E2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE2490E-7079-4FA1-821D-85AB8D60B043}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{605BC8C7-63F4-48BA-99A1-0E36A0F248CD}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802606E-119B-4066-959B-EB1BECE35D95}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E59A4A8F-05CD-4CBC-9DAC-75EC43F0C477}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48613DB-FA32-48ED-B297-68666B3F206C}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AD68C9A-90A2-4402-97B0-4E8EEAAF3197}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C79BC1E-6753-4623-8892-E7071D57BCA3}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4CBFBE4-7347-4ADE-B758-844C58AA50B8}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EDC82D-DD16-4B75-A044-2174FD64BD6A}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A0883D4F-7A33-495A-9007-9FD65445EB5F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE986469-7A0E-4309-8698-89910221A426}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3B846CDF-AE7D-49D8-AA17-24ECE0BBA512}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C425B1A-BCC4-43F9-B8B1-05511B945C9F}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{79556728-4942-44B1-AC07-F9BED8B351B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8C356139-DDE0-4C56-8192-09E6B7A4EBF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S04aH02,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S03aH04,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S04aH06,S05aH04,S06aH02,S06aH03</t>
+    <t>S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S05aH08,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH03,S04aH05,S04aH08,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH04,S01aH07,S02aH07</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S01aH10,S03aH02,S04aH02,S05aH08,S03aH09,S05aH09,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH09,S06aH09</t>
+    <t>S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08,S04aH08,S06aH01,S04aH02,S03aH09,S05aH09,S06aH09,S02aH01,S02aH10,S05aH02,S05aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH10,S03aH02,S01aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S01aH10,S03aH02,S04aH02,S05aH08,S03aH09,S05aH09,S04aH08,S06aH01,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S01aH01,S04aH01,S06aH02,S03aH01,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH09,S06aH09</v>
+        <v>S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08,S04aH08,S06aH01,S04aH02,S03aH09,S05aH09,S06aH09,S02aH01,S02aH10,S05aH02,S05aH08,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S01aH10,S03aH02,S01aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S04aH02,S03aH02,S04aH05,S04aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S05aH08,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S01aH06,S02aH03,S05aH07,S02aH02,S06aH06,S03aH04,S04aH03,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S04aH06,S05aH04,S06aH02,S06aH03</v>
+        <v>S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S05aH08,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH03,S05aH02,S05aH03,S05aH06,S04aH06,S05aH04,S06aH02,S06aH03,S04aH03,S04aH05,S04aH08,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH02,S01aH04,S01aH07,S02aH07</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FDE2490E-7079-4FA1-821D-85AB8D60B043}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41B926EC-AD2C-45DE-AAEF-196041EB553A}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0802606E-119B-4066-959B-EB1BECE35D95}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46277A38-E2C1-4507-BAED-4E9940538B4B}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F48613DB-FA32-48ED-B297-68666B3F206C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70F0D149-7699-4DA2-AD04-32BEB2A34D3F}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C79BC1E-6753-4623-8892-E7071D57BCA3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CC5A11B-1DEE-4133-9278-AD1D50D5B68E}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51EDC82D-DD16-4B75-A044-2174FD64BD6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1EA1AC9-639F-4A00-A851-6CBE8AF899F7}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE986469-7A0E-4309-8698-89910221A426}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58B833A6-E547-434C-AD70-60CE0A42015D}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C425B1A-BCC4-43F9-B8B1-05511B945C9F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD93EB27-2C3A-4DDA-A11F-375264F84F0B}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4F02755-E9AA-41CD-A998-E1B451F9E67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{13F18767-D751-4AD2-866B-AA899E91C779}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -750,13 +750,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S02aH04,S02aH05,S06aH07,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH03,S03aH04,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH06,S02aH03,S05aH07,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S05aH08</t>
+    <t>S01aH02,S04aH04,S03aH04,S04aH03,S01aH03,S05aH02,S05aH03,S05aH06,S01aH06,S02aH03,S05aH07,S03aH02,S05aH08,S04aH05,S04aH08,S02aH04,S02aH05,S06aH07,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH06,S05aH04,S06aH02,S06aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S04aH02</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH02,S03aH08,S03aH10,S06aH08,S05aH08,S01aH08,S02aH08,S03aH01,S01aH09,S01aH02,S05aH10,S02aH01,S02aH10,S05aH02,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S03aH09,S05aH09,S01aH01,S04aH01,S06aH02,S06aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01</t>
+    <t>S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02,S04aH02,S04aH08,S06aH01,S05aH08,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S06aH09,S03aH09,S05aH09,S03aH01,S01aH09,S01aH10,S03aH02</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1041,7 +1041,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C15AEB0-F12E-CB0A-AEDE-CBEC2F0239B3}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E4CE4BD0-DB63-90F7-B6B3-B84C4555CD76}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1096,7 +1096,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CD88581-B5CF-97AC-95ED-0B7AD7FD21D2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EAEDF25E-54AF-FE0F-8A33-E15084072202}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1151,7 +1151,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56142A8E-84FE-4297-D363-15FF4A7DB5B5}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{66648C1E-EF49-32C1-4C2E-680AA34970EE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1206,7 +1206,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B161CCF8-4ABC-87D8-6110-B4CADF61B623}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2A95065C-64FE-73AD-F68E-63B3172B374B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1261,7 +1261,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC841C67-28F1-C37E-C877-01F98B421DB1}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9DA3D3DF-08AB-8D6C-1DB6-119A883A7FEC}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1316,7 +1316,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D5073480-4C62-181D-9E4C-9D5FDE577940}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03D9D39C-716E-C6A4-7B8C-3E212D9EC576}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1371,7 +1371,7 @@
         <xdr:cNvPr id="3" name="Picture 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F9AFCEA2-A427-CCB4-452B-189E8F6A91C2}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C21189D2-C36F-6A0E-324A-7769E5E63E46}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1855,7 +1855,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S04aH02,S03aH08,S03aH10,S06aH08,S05aH08,S01aH08,S02aH08,S03aH01,S01aH09,S01aH02,S05aH10,S02aH01,S02aH10,S05aH02,S02aH09,S04aH09,S05aH01,S01aH10,S03aH02,S03aH09,S05aH09,S01aH01,S04aH01,S06aH02,S06aH09,S02aH02,S04aH10,S06aH10,S04aH08,S06aH01</v>
+        <v>S01aH08,S02aH08,S02aH09,S04aH09,S05aH01,S02aH01,S02aH10,S05aH02,S01aH01,S04aH01,S06aH02,S04aH02,S04aH08,S06aH01,S05aH08,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S06aH09,S03aH09,S05aH09,S03aH01,S01aH09,S01aH10,S03aH02</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1887,7 +1887,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH02,S02aH04,S02aH05,S06aH07,S04aH05,S04aH08,S01aH03,S05aH02,S05aH03,S05aH06,S01aH02,S04aH04,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH03,S03aH04,S04aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S01aH06,S02aH03,S05aH07,S04aH06,S05aH04,S06aH02,S06aH03,S03aH03,S05aH08</v>
+        <v>S01aH02,S04aH04,S03aH04,S04aH03,S01aH03,S05aH02,S05aH03,S05aH06,S01aH06,S02aH03,S05aH07,S03aH02,S05aH08,S04aH05,S04aH08,S02aH04,S02aH05,S06aH07,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S04aH06,S05aH04,S06aH02,S06aH03,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH04,S01aH07,S02aH07,S04aH02</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1987,7 +1987,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38C79B0A-BB54-4A41-807B-CE05E755BC73}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F354F586-281F-48FB-BE61-2C4D3DFE7405}">
   <dimension ref="A1:H20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -2174,7 +2174,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30C33E22-2801-4684-BF45-4009E1E8CDFF}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2BE6BC0-6BE5-4DB3-8C62-101A222057AB}">
   <dimension ref="A1:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -40660,7 +40660,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E27DB645-760D-42C5-9745-FE1411F1EE83}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B66CD601-3D8D-49AA-ADFE-CEA3D32F8377}">
   <dimension ref="A1:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -61797,7 +61797,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{72DC7A43-9111-4BA1-9B66-83BA794C33E5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FE02E4F0-311F-42DF-A8E0-69949255461B}">
   <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -62687,7 +62687,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABAB7216-AC49-44CE-B71C-A80F1FAF08EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BCF08D9E-BE7C-4B6B-8BDD-D19193276BC7}">
   <dimension ref="A1:H130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -64054,7 +64054,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{222CF273-A1AB-4834-8A3C-751ADD903DC2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{416D504F-7E22-4A93-BD9C-A90C3E49A0A4}">
   <dimension ref="A1:H70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
@@ -64761,7 +64761,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A715C52C-9487-4336-8001-BDF70D2194E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F4BD2666-37A8-4B23-AB52-1CCEC53BD216}">
   <dimension ref="A1:H184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A08A7BF-391C-4A05-80F8-32CA1F2D16A2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC41EC7F-2BBA-401F-8B1C-4E1BC65BEA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S02aH04,S02aH05,S06aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S04aH03,S03aH03,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S05aH08</t>
+    <t>S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH06,S02aH03,S05aH07,S04aH02,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S04aH05,S04aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S03aH08,S03aH10,S06aH08,S04aH02,S01aH02,S05aH10,S01aH09,S01aH10,S03aH02,S01aH08,S02aH08,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S06aH09,S05aH08,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S03aH01,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01</t>
+    <t>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02,S04aH08,S06aH01,S06aH09,S03aH01,S04aH02,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S05aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S03aH08,S03aH10,S06aH08,S04aH02,S01aH02,S05aH10,S01aH09,S01aH10,S03aH02,S01aH08,S02aH08,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S06aH09,S05aH08,S02aH01,S02aH10,S05aH02,S02aH02,S04aH10,S06aH10,S03aH01,S01aH01,S04aH01,S06aH02,S04aH08,S06aH01</v>
+        <v>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02,S04aH08,S06aH01,S06aH09,S03aH01,S04aH02,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S05aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S02aH04,S02aH05,S06aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH04,S01aH07,S02aH07,S01aH03,S05aH02,S05aH03,S05aH06,S04aH02,S01aH02,S04aH04,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S04aH06,S05aH04,S06aH02,S06aH03,S04aH05,S04aH08,S04aH03,S03aH03,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S05aH08</v>
+        <v>S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH06,S02aH03,S05aH07,S04aH02,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S04aH05,S04aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6604EEA-A39C-411B-A53E-C45BC33822D5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{092EFEFE-580F-49BF-A561-C47A1EB59F20}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{933AC750-D94B-4DB7-B90E-7696538BC935}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE581B6-B0CB-4165-A4A5-49764BE84364}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{09F7995A-7753-450A-BFF1-0AA16D37EB62}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35F9B18-D2D0-432F-9E0E-3A65FFCB3E8A}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{99782AC4-066A-4F3A-BD23-E6CB6865DC32}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800220BA-68EB-498B-A016-C040CFD45904}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D772309A-0617-42CD-820E-AFBFBF28352E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C8135-63B4-48AD-AFD7-4E0B8B24028B}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9473AE25-7B3E-482A-8C96-91CEAF5493D9}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7674F481-44FA-4524-A925-DEE3FD7AA987}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{69E5250E-A0F2-4482-8912-D13AB814FC2C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7924DED7-C680-4A60-898F-1F5FB6EAC9DE}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CC41EC7F-2BBA-401F-8B1C-4E1BC65BEA0B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1330BA4-B3BA-4041-8BFE-F8E8A70B45EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH06,S02aH03,S05aH07,S04aH02,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S04aH05,S04aH08</t>
+    <t>S03aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02,S04aH08,S06aH01,S06aH09,S03aH01,S04aH02,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S05aH08</t>
+    <t>S04aH02,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S06aH09,S01aH10,S03aH02,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S03aH09,S05aH09,S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S02aH02,S04aH10,S06aH10,S01aH09,S03aH08,S03aH10,S06aH08,S01aH08,S02aH08,S02aH01,S02aH10,S05aH02,S01aH02,S05aH10,S01aH01,S04aH01,S06aH02,S01aH10,S03aH02,S04aH08,S06aH01,S06aH09,S03aH01,S04aH02,S03aH09,S05aH09,S02aH09,S04aH09,S05aH01,S05aH08</v>
+        <v>S04aH02,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S06aH09,S01aH10,S03aH02,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S03aH09,S05aH09,S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH03,S01aH04,S01aH07,S02aH07,S02aH04,S02aH05,S06aH07,S01aH02,S04aH04,S04aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH06,S02aH03,S05aH07,S04aH02,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S03aH02,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S04aH05,S04aH08</v>
+        <v>S03aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{092EFEFE-580F-49BF-A561-C47A1EB59F20}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21296C7-15FE-4CC2-A81E-1535EF380E6D}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9EE581B6-B0CB-4165-A4A5-49764BE84364}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68FA35E7-6167-41EC-9E78-87923AE26D40}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E35F9B18-D2D0-432F-9E0E-3A65FFCB3E8A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846FC149-1BA5-4317-A574-62CC4ABB4D23}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{800220BA-68EB-498B-A016-C040CFD45904}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950E7F50-DAA6-40C2-A706-82E7571998ED}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B2C8135-63B4-48AD-AFD7-4E0B8B24028B}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715E12A6-2C86-4D76-B496-802A9D45AD0E}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7674F481-44FA-4524-A925-DEE3FD7AA987}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52136F89-3E4B-41E6-983D-7060A553C0EA}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7924DED7-C680-4A60-898F-1F5FB6EAC9DE}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0124FCC0-00A7-4DB8-A07B-BEEFF5ED57ED}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
+++ b/VerveStacks_POL_grids_kan/SuppXLS/Scen_TSParameters_ts_60c.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_POL_grids_kan\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D1330BA4-B3BA-4041-8BFE-F8E8A70B45EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6363C9B2-BB32-4512-825B-9EFED649A80D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="7" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -747,13 +747,13 @@
     <t>D</t>
   </si>
   <si>
-    <t>S03aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06</t>
+    <t>S04aH02,S02aH04,S02aH05,S06aH07,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S01aH06,S02aH03,S05aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH02,S04aH04,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08</t>
   </si>
   <si>
     <t>N</t>
   </si>
   <si>
-    <t>S04aH02,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S06aH09,S01aH10,S03aH02,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S03aH09,S05aH09,S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08</t>
+    <t>S01aH10,S03aH02,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S06aH09,S03aH01,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S02aH09,S04aH09,S05aH01,S01aH01,S04aH01,S06aH02,S04aH02,S01aH02,S05aH10,S01aH08,S02aH08,S04aH08,S06aH01,S03aH09,S05aH09</t>
   </si>
   <si>
     <t>elc_buildings</t>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="H23" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,3,FALSE)</f>
-        <v>S04aH02,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S04aH08,S06aH01,S06aH09,S01aH10,S03aH02,S02aH09,S04aH09,S05aH01,S02aH02,S04aH10,S06aH10,S01aH02,S05aH10,S03aH09,S05aH09,S03aH01,S01aH01,S04aH01,S06aH02,S01aH08,S02aH08,S03aH08,S03aH10,S06aH08</v>
+        <v>S01aH10,S03aH02,S03aH08,S03aH10,S06aH08,S02aH02,S04aH10,S06aH10,S06aH09,S03aH01,S05aH08,S01aH09,S02aH01,S02aH10,S05aH02,S02aH09,S04aH09,S05aH01,S01aH01,S04aH01,S06aH02,S04aH02,S01aH02,S05aH10,S01aH08,S02aH08,S04aH08,S06aH01,S03aH09,S05aH09</v>
       </c>
       <c r="I23">
         <f>1+I24</f>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H24" t="str">
         <f>HLOOKUP($A$10,$D$10:$CU$12,2,FALSE)</f>
-        <v>S03aH02,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S05aH08,S04aH06,S05aH04,S06aH02,S06aH03,S04aH02,S03aH04,S03aH03,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08,S02aH02,S06aH06,S01aH06,S02aH03,S05aH07,S01aH02,S04aH04,S02aH04,S02aH05,S06aH07,S01aH03,S05aH02,S05aH03,S05aH06</v>
+        <v>S04aH02,S02aH04,S02aH05,S06aH07,S03aH03,S04aH06,S05aH04,S06aH02,S06aH03,S02aH02,S06aH06,S04aH05,S04aH08,S01aH04,S01aH07,S02aH07,S04aH03,S03aH04,S01aH03,S05aH02,S05aH03,S05aH06,S01aH06,S02aH03,S05aH07,S03aH02,S01aH05,S01aH08,S02aH08,S03aH06,S03aH07,S06aH05,S01aH02,S04aH04,S05aH08,S02aH06,S03aH05,S03aH08,S04aH07,S05aH05,S06aH04,S06aH08</v>
       </c>
       <c r="I24">
         <f>-$I$17</f>
@@ -1476,7 +1476,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A21296C7-15FE-4CC2-A81E-1535EF380E6D}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BA6C5939-7A97-4E3D-B72B-FCB60DBD8104}">
   <dimension ref="A9:G20"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -1620,7 +1620,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{68FA35E7-6167-41EC-9E78-87923AE26D40}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2178D47F-692F-4963-A786-35D151EEFF58}">
   <dimension ref="B9:O1210"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -40082,7 +40082,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{846FC149-1BA5-4317-A574-62CC4ABB4D23}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{827005A0-429A-4B5E-834D-2B674FC19089}">
   <dimension ref="B9:IV60"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -61135,7 +61135,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{950E7F50-DAA6-40C2-A706-82E7571998ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22ACD2D9-91F0-4C78-82B1-4CB4BF86AD75}">
   <dimension ref="B9:E70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -62005,7 +62005,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{715E12A6-2C86-4D76-B496-802A9D45AD0E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77BE535-39ED-4C05-8CEC-EFF9EF2B75BF}">
   <dimension ref="B9:D130"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -63352,7 +63352,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{52136F89-3E4B-41E6-983D-7060A553C0EA}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DD3EBB-D555-4430-85EA-09F79E95F98D}">
   <dimension ref="B9:D70"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -64039,7 +64039,7 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0124FCC0-00A7-4DB8-A07B-BEEFF5ED57ED}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C2ED2FEF-485B-4790-9671-7E7B8F928D6E}">
   <dimension ref="B9:E184"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
